--- a/simulator.xlsx
+++ b/simulator.xlsx
@@ -6,7 +6,7 @@
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t xml:space="preserve">8-BIT VON NEUMANN CPU SIMULATOR</t>
   </si>
@@ -72,15 +72,27 @@
     <t>00h</t>
   </si>
   <si>
+    <t>0F</t>
+  </si>
+  <si>
     <t>MDR</t>
   </si>
   <si>
+    <t>1F</t>
+  </si>
+  <si>
     <t>10h</t>
   </si>
   <si>
+    <t>1A</t>
+  </si>
+  <si>
     <t>AX</t>
   </si>
   <si>
+    <t>2C</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reserved Area</t>
   </si>
   <si>
@@ -90,6 +102,9 @@
     <t>BX</t>
   </si>
   <si>
+    <t>AB</t>
+  </si>
+  <si>
     <t>30h</t>
   </si>
   <si>
@@ -166,6 +181,9 @@
   </si>
   <si>
     <t>F0h</t>
+  </si>
+  <si>
+    <t>FF</t>
   </si>
   <si>
     <t xml:space="preserve">Delay (ms):</t>
@@ -307,8 +325,8 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -317,36 +335,36 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right/>
+      <right style="none"/>
       <top style="thin">
         <color theme="1"/>
       </top>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
         <color theme="1"/>
       </top>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
+      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -356,7 +374,7 @@
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -365,17 +383,17 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -422,9 +440,6 @@
     </xf>
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1066,10 +1081,14 @@
         <v>5</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D6" s="4">
+        <v>10101</v>
+      </c>
+      <c r="E6" s="4">
+        <v>21</v>
+      </c>
       <c r="J6" s="5" t="s">
         <v>6</v>
       </c>
@@ -1095,10 +1114,14 @@
         <v>7</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
       <c r="J7" s="4" t="s">
         <v>8</v>
       </c>
@@ -1155,201 +1178,449 @@
       <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
       <c r="I8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
+      <c r="K8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7">
+        <v>0</v>
+      </c>
+      <c r="W8" s="7">
+        <v>0</v>
+      </c>
+      <c r="X8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="14.25">
       <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4">
+        <v>11111</v>
+      </c>
+      <c r="E9" s="4">
+        <v>31</v>
+      </c>
       <c r="I9" s="6"/>
       <c r="J9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7">
+        <v>0</v>
+      </c>
+      <c r="T9" s="7">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="V9" s="7">
+        <v>0</v>
+      </c>
+      <c r="W9" s="7">
+        <v>0</v>
+      </c>
+      <c r="X9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" ht="14.25">
       <c r="B10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="4">
+        <v>101100</v>
+      </c>
+      <c r="E10" s="4">
+        <v>44</v>
+      </c>
       <c r="I10" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
+        <v>26</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
+      <c r="S10" s="9">
+        <v>0</v>
+      </c>
+      <c r="T10" s="9">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9">
+        <v>0</v>
+      </c>
+      <c r="V10" s="9">
+        <v>0</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="14.25">
       <c r="B11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="4">
+        <v>10101011</v>
+      </c>
+      <c r="E11" s="4">
+        <v>171</v>
+      </c>
       <c r="I11" s="10"/>
       <c r="J11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9">
+        <v>0</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" ht="14.25">
       <c r="I12" s="10"/>
       <c r="J12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
+      </c>
+      <c r="S12" s="9">
+        <v>0</v>
+      </c>
+      <c r="T12" s="9">
+        <v>0</v>
+      </c>
+      <c r="U12" s="9">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" ht="14.25">
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="I13" s="10"/>
       <c r="J13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0</v>
+      </c>
+      <c r="S13" s="9">
+        <v>0</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="14.25">
       <c r="B14" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C14" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="13"/>
       <c r="I14" s="10"/>
       <c r="J14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9">
+        <v>0</v>
+      </c>
+      <c r="V14" s="9">
+        <v>0</v>
+      </c>
+      <c r="W14" s="9">
+        <v>0</v>
+      </c>
+      <c r="X14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
       <c r="B15" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11">
         <v>0</v>
@@ -1358,766 +1629,1054 @@
       <c r="E15" s="13"/>
       <c r="I15" s="14"/>
       <c r="J15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9">
+        <v>0</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9">
+        <v>0</v>
+      </c>
+      <c r="S15" s="9">
+        <v>0</v>
+      </c>
+      <c r="T15" s="9">
+        <v>0</v>
+      </c>
+      <c r="U15" s="9">
+        <v>0</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0</v>
+      </c>
+      <c r="W15" s="9">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" ht="14.25">
       <c r="B16" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C16" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="13"/>
       <c r="I16" s="8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
+        <v>39</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>0</v>
+      </c>
+      <c r="N16" s="15">
+        <v>0</v>
+      </c>
+      <c r="O16" s="15">
+        <v>0</v>
+      </c>
+      <c r="P16" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>0</v>
+      </c>
+      <c r="R16" s="15">
+        <v>0</v>
+      </c>
+      <c r="S16" s="15">
+        <v>0</v>
+      </c>
+      <c r="T16" s="15">
+        <v>0</v>
+      </c>
+      <c r="U16" s="15">
+        <v>0</v>
+      </c>
+      <c r="V16" s="15">
+        <v>0</v>
+      </c>
+      <c r="W16" s="15">
+        <v>0</v>
+      </c>
+      <c r="X16" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" ht="14.25">
       <c r="I17" s="10"/>
       <c r="J17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="K17" s="15">
+        <v>0</v>
+      </c>
+      <c r="L17" s="15">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15">
+        <v>0</v>
+      </c>
+      <c r="N17" s="15">
+        <v>0</v>
+      </c>
+      <c r="O17" s="15">
+        <v>0</v>
+      </c>
+      <c r="P17" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="15">
+        <v>0</v>
+      </c>
+      <c r="R17" s="15">
+        <v>0</v>
+      </c>
+      <c r="S17" s="15">
+        <v>0</v>
+      </c>
+      <c r="T17" s="15">
+        <v>0</v>
+      </c>
+      <c r="U17" s="15">
+        <v>0</v>
+      </c>
+      <c r="V17" s="15">
+        <v>0</v>
+      </c>
+      <c r="W17" s="15">
+        <v>0</v>
+      </c>
+      <c r="X17" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" ht="14.25">
       <c r="B18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+        <v>41</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
       <c r="I18" s="10"/>
       <c r="J18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
+        <v>43</v>
+      </c>
+      <c r="K18" s="15">
+        <v>0</v>
+      </c>
+      <c r="L18" s="15">
+        <v>0</v>
+      </c>
+      <c r="M18" s="15">
+        <v>0</v>
+      </c>
+      <c r="N18" s="15">
+        <v>0</v>
+      </c>
+      <c r="O18" s="15">
+        <v>0</v>
+      </c>
+      <c r="P18" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="15">
+        <v>0</v>
+      </c>
+      <c r="R18" s="15">
+        <v>0</v>
+      </c>
+      <c r="S18" s="15">
+        <v>0</v>
+      </c>
+      <c r="T18" s="15">
+        <v>0</v>
+      </c>
+      <c r="U18" s="15">
+        <v>0</v>
+      </c>
+      <c r="V18" s="15">
+        <v>0</v>
+      </c>
+      <c r="W18" s="15">
+        <v>0</v>
+      </c>
+      <c r="X18" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
       <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="18">
-        <v>0</v>
-      </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+        <v>44</v>
+      </c>
+      <c r="C19" s="17">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
       <c r="I19" s="10"/>
       <c r="J19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
-      <c r="Z19" s="15"/>
+        <v>45</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0</v>
+      </c>
+      <c r="N19" s="15">
+        <v>0</v>
+      </c>
+      <c r="O19" s="15">
+        <v>0</v>
+      </c>
+      <c r="P19" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="15">
+        <v>0</v>
+      </c>
+      <c r="R19" s="15">
+        <v>0</v>
+      </c>
+      <c r="S19" s="15">
+        <v>0</v>
+      </c>
+      <c r="T19" s="15">
+        <v>0</v>
+      </c>
+      <c r="U19" s="15">
+        <v>0</v>
+      </c>
+      <c r="V19" s="15">
+        <v>0</v>
+      </c>
+      <c r="W19" s="15">
+        <v>0</v>
+      </c>
+      <c r="X19" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" ht="14.25">
       <c r="I20" s="10"/>
       <c r="J20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
+        <v>46</v>
+      </c>
+      <c r="K20" s="15">
+        <v>0</v>
+      </c>
+      <c r="L20" s="15">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15">
+        <v>0</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0</v>
+      </c>
+      <c r="O20" s="15">
+        <v>0</v>
+      </c>
+      <c r="P20" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="15">
+        <v>0</v>
+      </c>
+      <c r="R20" s="15">
+        <v>0</v>
+      </c>
+      <c r="S20" s="15">
+        <v>0</v>
+      </c>
+      <c r="T20" s="15">
+        <v>0</v>
+      </c>
+      <c r="U20" s="15">
+        <v>0</v>
+      </c>
+      <c r="V20" s="15">
+        <v>0</v>
+      </c>
+      <c r="W20" s="15">
+        <v>0</v>
+      </c>
+      <c r="X20" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="B21" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="20"/>
+      <c r="B21" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="19"/>
       <c r="I21" s="10"/>
       <c r="J21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
+        <v>49</v>
+      </c>
+      <c r="K21" s="15">
+        <v>0</v>
+      </c>
+      <c r="L21" s="15">
+        <v>0</v>
+      </c>
+      <c r="M21" s="15">
+        <v>0</v>
+      </c>
+      <c r="N21" s="15">
+        <v>0</v>
+      </c>
+      <c r="O21" s="15">
+        <v>0</v>
+      </c>
+      <c r="P21" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="15">
+        <v>0</v>
+      </c>
+      <c r="R21" s="15">
+        <v>0</v>
+      </c>
+      <c r="S21" s="15">
+        <v>0</v>
+      </c>
+      <c r="T21" s="15">
+        <v>0</v>
+      </c>
+      <c r="U21" s="15">
+        <v>0</v>
+      </c>
+      <c r="V21" s="15">
+        <v>0</v>
+      </c>
+      <c r="W21" s="15">
+        <v>0</v>
+      </c>
+      <c r="X21" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" ht="14.25">
-      <c r="B22" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="19"/>
+      <c r="B22" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="18"/>
       <c r="I22" s="10"/>
       <c r="J22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="15"/>
-      <c r="T22" s="15"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
+        <v>52</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0</v>
+      </c>
+      <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
+        <v>0</v>
+      </c>
+      <c r="N22" s="15">
+        <v>0</v>
+      </c>
+      <c r="O22" s="15">
+        <v>0</v>
+      </c>
+      <c r="P22" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="15">
+        <v>0</v>
+      </c>
+      <c r="R22" s="15">
+        <v>0</v>
+      </c>
+      <c r="S22" s="15">
+        <v>0</v>
+      </c>
+      <c r="T22" s="15">
+        <v>0</v>
+      </c>
+      <c r="U22" s="15">
+        <v>0</v>
+      </c>
+      <c r="V22" s="15">
+        <v>0</v>
+      </c>
+      <c r="W22" s="15">
+        <v>0</v>
+      </c>
+      <c r="X22" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="15">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="B23" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
+      <c r="B23" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
       <c r="I23" s="14"/>
       <c r="J23" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
+        <v>0</v>
+      </c>
+      <c r="N23" s="15">
+        <v>0</v>
+      </c>
+      <c r="O23" s="15">
+        <v>0</v>
+      </c>
+      <c r="P23" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="15">
+        <v>0</v>
+      </c>
+      <c r="R23" s="15">
+        <v>0</v>
+      </c>
+      <c r="S23" s="15">
+        <v>0</v>
+      </c>
+      <c r="T23" s="15">
+        <v>0</v>
+      </c>
+      <c r="U23" s="15">
+        <v>0</v>
+      </c>
+      <c r="V23" s="15">
+        <v>0</v>
+      </c>
+      <c r="W23" s="15">
+        <v>0</v>
+      </c>
+      <c r="X23" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="15" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="24" ht="14.25">
-      <c r="B24" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="18">
+      <c r="B24" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="17">
         <v>500</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="B26" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
+      <c r="B26" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="B27" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="22" t="s">
+      <c r="B27" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="I27" s="22" t="s">
+      <c r="G27" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="J27" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="22"/>
-      <c r="X27" s="22"/>
-      <c r="Y27" s="22"/>
-      <c r="Z27" s="22"/>
+      <c r="I27" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="21"/>
+      <c r="V27" s="21"/>
+      <c r="W27" s="21"/>
+      <c r="X27" s="21"/>
+      <c r="Y27" s="21"/>
+      <c r="Z27" s="21"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="23"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="23"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="24"/>
-      <c r="V29" s="24"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="23"/>
+      <c r="X29" s="23"/>
+      <c r="Y29" s="23"/>
+      <c r="Z29" s="23"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="24"/>
-      <c r="R30" s="24"/>
-      <c r="S30" s="24"/>
-      <c r="T30" s="24"/>
-      <c r="U30" s="24"/>
-      <c r="V30" s="24"/>
-      <c r="W30" s="24"/>
-      <c r="X30" s="24"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="24"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="23"/>
+      <c r="X30" s="23"/>
+      <c r="Y30" s="23"/>
+      <c r="Z30" s="23"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="24"/>
-      <c r="R31" s="24"/>
-      <c r="S31" s="24"/>
-      <c r="T31" s="24"/>
-      <c r="U31" s="24"/>
-      <c r="V31" s="24"/>
-      <c r="W31" s="24"/>
-      <c r="X31" s="24"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="24"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="23"/>
+      <c r="Y31" s="23"/>
+      <c r="Z31" s="23"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="24"/>
-      <c r="Q32" s="24"/>
-      <c r="R32" s="24"/>
-      <c r="S32" s="24"/>
-      <c r="T32" s="24"/>
-      <c r="U32" s="24"/>
-      <c r="V32" s="24"/>
-      <c r="W32" s="24"/>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="24"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="23"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="23"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="23"/>
+      <c r="V32" s="23"/>
+      <c r="W32" s="23"/>
+      <c r="X32" s="23"/>
+      <c r="Y32" s="23"/>
+      <c r="Z32" s="23"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="24"/>
-      <c r="R33" s="24"/>
-      <c r="S33" s="24"/>
-      <c r="T33" s="24"/>
-      <c r="U33" s="24"/>
-      <c r="V33" s="24"/>
-      <c r="W33" s="24"/>
-      <c r="X33" s="24"/>
-      <c r="Y33" s="24"/>
-      <c r="Z33" s="24"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="23"/>
+      <c r="O33" s="23"/>
+      <c r="P33" s="23"/>
+      <c r="Q33" s="23"/>
+      <c r="R33" s="23"/>
+      <c r="S33" s="23"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="23"/>
+      <c r="V33" s="23"/>
+      <c r="W33" s="23"/>
+      <c r="X33" s="23"/>
+      <c r="Y33" s="23"/>
+      <c r="Z33" s="23"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="24"/>
-      <c r="R34" s="24"/>
-      <c r="S34" s="24"/>
-      <c r="T34" s="24"/>
-      <c r="U34" s="24"/>
-      <c r="V34" s="24"/>
-      <c r="W34" s="24"/>
-      <c r="X34" s="24"/>
-      <c r="Y34" s="24"/>
-      <c r="Z34" s="24"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
+      <c r="M34" s="23"/>
+      <c r="N34" s="23"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="23"/>
+      <c r="U34" s="23"/>
+      <c r="V34" s="23"/>
+      <c r="W34" s="23"/>
+      <c r="X34" s="23"/>
+      <c r="Y34" s="23"/>
+      <c r="Z34" s="23"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="24"/>
-      <c r="U35" s="24"/>
-      <c r="V35" s="24"/>
-      <c r="W35" s="24"/>
-      <c r="X35" s="24"/>
-      <c r="Y35" s="24"/>
-      <c r="Z35" s="24"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="23"/>
+      <c r="U35" s="23"/>
+      <c r="V35" s="23"/>
+      <c r="W35" s="23"/>
+      <c r="X35" s="23"/>
+      <c r="Y35" s="23"/>
+      <c r="Z35" s="23"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="24"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="23"/>
+      <c r="U36" s="23"/>
+      <c r="V36" s="23"/>
+      <c r="W36" s="23"/>
+      <c r="X36" s="23"/>
+      <c r="Y36" s="23"/>
+      <c r="Z36" s="23"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="24"/>
-      <c r="U37" s="24"/>
-      <c r="V37" s="24"/>
-      <c r="W37" s="24"/>
-      <c r="X37" s="24"/>
-      <c r="Y37" s="24"/>
-      <c r="Z37" s="24"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="23"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="23"/>
+      <c r="S37" s="23"/>
+      <c r="T37" s="23"/>
+      <c r="U37" s="23"/>
+      <c r="V37" s="23"/>
+      <c r="W37" s="23"/>
+      <c r="X37" s="23"/>
+      <c r="Y37" s="23"/>
+      <c r="Z37" s="23"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="24"/>
-      <c r="U38" s="24"/>
-      <c r="V38" s="24"/>
-      <c r="W38" s="24"/>
-      <c r="X38" s="24"/>
-      <c r="Y38" s="24"/>
-      <c r="Z38" s="24"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="23"/>
+      <c r="T38" s="23"/>
+      <c r="U38" s="23"/>
+      <c r="V38" s="23"/>
+      <c r="W38" s="23"/>
+      <c r="X38" s="23"/>
+      <c r="Y38" s="23"/>
+      <c r="Z38" s="23"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="24"/>
-      <c r="Q39" s="24"/>
-      <c r="R39" s="24"/>
-      <c r="S39" s="24"/>
-      <c r="T39" s="24"/>
-      <c r="U39" s="24"/>
-      <c r="V39" s="24"/>
-      <c r="W39" s="24"/>
-      <c r="X39" s="24"/>
-      <c r="Y39" s="24"/>
-      <c r="Z39" s="24"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="23"/>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="23"/>
+      <c r="S39" s="23"/>
+      <c r="T39" s="23"/>
+      <c r="U39" s="23"/>
+      <c r="V39" s="23"/>
+      <c r="W39" s="23"/>
+      <c r="X39" s="23"/>
+      <c r="Y39" s="23"/>
+      <c r="Z39" s="23"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="24"/>
-      <c r="T40" s="24"/>
-      <c r="U40" s="24"/>
-      <c r="V40" s="24"/>
-      <c r="W40" s="24"/>
-      <c r="X40" s="24"/>
-      <c r="Y40" s="24"/>
-      <c r="Z40" s="24"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="23"/>
+      <c r="W40" s="23"/>
+      <c r="X40" s="23"/>
+      <c r="Y40" s="23"/>
+      <c r="Z40" s="23"/>
     </row>
     <row r="41" ht="14.25">
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="24"/>
-      <c r="Q41" s="24"/>
-      <c r="R41" s="24"/>
-      <c r="S41" s="24"/>
-      <c r="T41" s="24"/>
-      <c r="U41" s="24"/>
-      <c r="V41" s="24"/>
-      <c r="W41" s="24"/>
-      <c r="X41" s="24"/>
-      <c r="Y41" s="24"/>
-      <c r="Z41" s="24"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="23"/>
+      <c r="Q41" s="23"/>
+      <c r="R41" s="23"/>
+      <c r="S41" s="23"/>
+      <c r="T41" s="23"/>
+      <c r="U41" s="23"/>
+      <c r="V41" s="23"/>
+      <c r="W41" s="23"/>
+      <c r="X41" s="23"/>
+      <c r="Y41" s="23"/>
+      <c r="Z41" s="23"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
-      <c r="R42" s="24"/>
-      <c r="S42" s="24"/>
-      <c r="T42" s="24"/>
-      <c r="U42" s="24"/>
-      <c r="V42" s="24"/>
-      <c r="W42" s="24"/>
-      <c r="X42" s="24"/>
-      <c r="Y42" s="24"/>
-      <c r="Z42" s="24"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
+      <c r="P42" s="23"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="23"/>
+      <c r="S42" s="23"/>
+      <c r="T42" s="23"/>
+      <c r="U42" s="23"/>
+      <c r="V42" s="23"/>
+      <c r="W42" s="23"/>
+      <c r="X42" s="23"/>
+      <c r="Y42" s="23"/>
+      <c r="Z42" s="23"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="24"/>
-      <c r="N43" s="24"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="24"/>
-      <c r="Q43" s="24"/>
-      <c r="R43" s="24"/>
-      <c r="S43" s="24"/>
-      <c r="T43" s="24"/>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="24"/>
-      <c r="Y43" s="24"/>
-      <c r="Z43" s="24"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="23"/>
+      <c r="S43" s="23"/>
+      <c r="T43" s="23"/>
+      <c r="U43" s="23"/>
+      <c r="V43" s="23"/>
+      <c r="W43" s="23"/>
+      <c r="X43" s="23"/>
+      <c r="Y43" s="23"/>
+      <c r="Z43" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="35">

--- a/simulator.xlsx
+++ b/simulator.xlsx
@@ -16,11 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">8-BIT VON NEUMANN CPU SIMULATOR</t>
   </si>
   <si>
+    <t>i</t>
+  </si>
+  <si>
     <t>Register</t>
   </si>
   <si>
@@ -36,6 +39,9 @@
     <t>PC</t>
   </si>
   <si>
+    <t>0B</t>
+  </si>
+  <si>
     <t>RAM</t>
   </si>
   <si>
@@ -66,33 +72,24 @@
     <t>MAR</t>
   </si>
   <si>
+    <t>0A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Code Segment</t>
   </si>
   <si>
     <t>00h</t>
   </si>
   <si>
-    <t>0F</t>
-  </si>
-  <si>
     <t>MDR</t>
   </si>
   <si>
-    <t>1F</t>
-  </si>
-  <si>
     <t>10h</t>
   </si>
   <si>
-    <t>1A</t>
-  </si>
-  <si>
     <t>AX</t>
   </si>
   <si>
-    <t>2C</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reserved Area</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
     <t>BX</t>
   </si>
   <si>
-    <t>AB</t>
-  </si>
-  <si>
     <t>30h</t>
   </si>
   <si>
@@ -181,9 +175,6 @@
   </si>
   <si>
     <t>F0h</t>
-  </si>
-  <si>
-    <t>FF</t>
   </si>
   <si>
     <t xml:space="preserve">Delay (ms):</t>
@@ -1062,35 +1053,40 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
+    <row r="4" ht="14.25">
+      <c r="O4" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="5" ht="14.25">
       <c r="B5" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4">
-        <v>15</v>
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="D6" s="4">
-        <v>10101</v>
+        <v>1011</v>
       </c>
       <c r="E6" s="4">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -1111,19 +1107,19 @@
     </row>
     <row r="7" ht="14.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K7" s="4">
         <v>0</v>
@@ -1156,45 +1152,45 @@
         <v>9</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
       </c>
       <c r="L8" s="7">
         <v>0</v>
@@ -1224,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="U8" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="7">
         <v>0</v>
@@ -1244,20 +1240,20 @@
     </row>
     <row r="9" ht="14.25">
       <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
       </c>
       <c r="D9" s="4">
-        <v>11111</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" s="7">
         <v>0</v>
@@ -1289,8 +1285,8 @@
       <c r="T9" s="7">
         <v>0</v>
       </c>
-      <c r="U9" s="7" t="s">
-        <v>22</v>
+      <c r="U9" s="7">
+        <v>0</v>
       </c>
       <c r="V9" s="7">
         <v>0</v>
@@ -1312,20 +1308,20 @@
       <c r="B10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="4">
-        <v>101100</v>
-      </c>
-      <c r="E10" s="4">
-        <v>44</v>
-      </c>
-      <c r="I10" s="8" t="s">
+      <c r="J10" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="K10" s="9">
         <v>0</v>
@@ -1378,20 +1374,20 @@
     </row>
     <row r="11" ht="14.25">
       <c r="B11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
       </c>
       <c r="D11" s="4">
-        <v>10101011</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K11" s="9">
         <v>0</v>
@@ -1445,7 +1441,7 @@
     <row r="12" ht="14.25">
       <c r="I12" s="10"/>
       <c r="J12" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K12" s="9">
         <v>0</v>
@@ -1498,14 +1494,14 @@
     </row>
     <row r="13" ht="14.25">
       <c r="B13" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="I13" s="10"/>
       <c r="J13" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K13" s="9">
         <v>0</v>
@@ -1558,16 +1554,16 @@
     </row>
     <row r="14" ht="14.25">
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="13"/>
       <c r="I14" s="10"/>
       <c r="J14" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K14" s="9">
         <v>0</v>
@@ -1620,7 +1616,7 @@
     </row>
     <row r="15" ht="14.25">
       <c r="B15" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="11">
         <v>0</v>
@@ -1629,7 +1625,7 @@
       <c r="E15" s="13"/>
       <c r="I15" s="14"/>
       <c r="J15" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K15" s="9">
         <v>0</v>
@@ -1682,18 +1678,18 @@
     </row>
     <row r="16" ht="14.25">
       <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="13"/>
       <c r="I16" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
         <v>0</v>
@@ -1747,7 +1743,7 @@
     <row r="17" ht="14.25">
       <c r="I17" s="10"/>
       <c r="J17" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K17" s="15">
         <v>0</v>
@@ -1800,16 +1796,16 @@
     </row>
     <row r="18" ht="14.25">
       <c r="B18" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="I18" s="10"/>
       <c r="J18" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
         <v>0</v>
@@ -1862,7 +1858,7 @@
     </row>
     <row r="19" ht="14.25">
       <c r="B19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -1871,7 +1867,7 @@
       <c r="E19" s="17"/>
       <c r="I19" s="10"/>
       <c r="J19" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K19" s="15">
         <v>0</v>
@@ -1925,7 +1921,7 @@
     <row r="20" ht="14.25">
       <c r="I20" s="10"/>
       <c r="J20" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
@@ -1978,16 +1974,16 @@
     </row>
     <row r="21" ht="14.25">
       <c r="B21" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E21" s="19"/>
       <c r="I21" s="10"/>
       <c r="J21" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K21" s="15">
         <v>0</v>
@@ -2040,16 +2036,16 @@
     </row>
     <row r="22" ht="14.25">
       <c r="B22" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E22" s="18"/>
       <c r="I22" s="10"/>
       <c r="J22" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K22" s="15">
         <v>0</v>
@@ -2102,14 +2098,14 @@
     </row>
     <row r="23" ht="14.25">
       <c r="B23" s="18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="I23" s="14"/>
       <c r="J23" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K23" s="15">
         <v>0</v>
@@ -2156,13 +2152,13 @@
       <c r="Y23" s="15">
         <v>0</v>
       </c>
-      <c r="Z23" s="15" t="s">
-        <v>55</v>
+      <c r="Z23" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="B24" s="17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C24" s="17">
         <v>500</v>
@@ -2172,7 +2168,7 @@
     </row>
     <row r="26" ht="14.25">
       <c r="B26" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
@@ -2201,34 +2197,34 @@
     </row>
     <row r="27" ht="14.25">
       <c r="B27" s="21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
